--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129448595</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104191</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stålråd AV4413, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>601853</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6570654</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Emma Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Leif Andersson, Robert Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129448595</v>
       </c>
       <c r="B3" t="n">
-        <v>104191</v>
+        <v>104193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129448595</v>
       </c>
       <c r="B3" t="n">
-        <v>104193</v>
+        <v>104197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129448595</v>
       </c>
       <c r="B3" t="n">
-        <v>104197</v>
+        <v>104207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129448595</v>
       </c>
       <c r="B3" t="n">
-        <v>104207</v>
+        <v>104210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Leif Andersson, Robert Ennerfelt</t>
+          <t>Robert Ennerfelt, Leif Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Robert Ennerfelt, Leif Andersson</t>
+          <t>Leif Andersson, Robert Ennerfelt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129448595</v>
       </c>
       <c r="B3" t="n">
-        <v>104210</v>
+        <v>104239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129448595</v>
       </c>
       <c r="B3" t="n">
-        <v>104239</v>
+        <v>104251</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129448595</v>
       </c>
       <c r="B3" t="n">
-        <v>104251</v>
+        <v>104252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129448595</v>
       </c>
       <c r="B3" t="n">
-        <v>104252</v>
+        <v>104257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Leif Andersson, Robert Ennerfelt</t>
+          <t>Robert Ennerfelt, Leif Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129448595</v>
       </c>
       <c r="B3" t="n">
-        <v>104257</v>
+        <v>104261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129448595</v>
       </c>
       <c r="B3" t="n">
-        <v>104261</v>
+        <v>104263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50915-2025 artfynd.xlsx
+++ b/artfynd/A 50915-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>79740550</v>
       </c>
       <c r="B2" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601862.8583812469</v>
+        <v>601863</v>
       </c>
       <c r="R2" t="n">
-        <v>6570649.094864776</v>
+        <v>6570649</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-08-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +780,7 @@
         <v>129448595</v>
       </c>
       <c r="B3" t="n">
-        <v>104263</v>
+        <v>104639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
